--- a/input_data/LV_Database_GMD.xlsx
+++ b/input_data/LV_Database_GMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Studium\Desktop\Launch_Reentry_Data\Paper_LEAT\input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Studium\Desktop\Launch_Reentry_Data\LEAT-1.0.0\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B023A5A-DEEB-430B-AE22-4893466044A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9B8DA9-AF88-400A-84BD-B7CE75B16A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LV_Database" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="README - How to enter data" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Engine!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">LV_Database!$A$1:$BM$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Engine!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">LV_Database!$A$1:$BN$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="176">
   <si>
     <t>sheet: LV_Database</t>
   </si>
@@ -239,9 +239,6 @@
     <t>engine</t>
   </si>
   <si>
-    <t>d_exit</t>
-  </si>
-  <si>
     <t>engine_cycle</t>
   </si>
   <si>
@@ -564,6 +561,12 @@
   </si>
   <si>
     <t>https://www.eucass.eu/doi/EUCASS2019-0639.pdf, https://www.safran-group.com/products-services/vulcain-21-hot-gas-valve-vgc-21</t>
+  </si>
+  <si>
+    <t>A_e_A_R</t>
+  </si>
+  <si>
+    <t>Factor of enigne exhaust area to rocket area</t>
   </si>
 </sst>
 </file>
@@ -672,7 +675,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -969,6 +972,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -976,7 +1003,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1220,6 +1247,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1683,7 +1716,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:BU8"/>
+  <dimension ref="A1:BV8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
@@ -1691,55 +1724,56 @@
     <col min="3" max="3" width="6" style="63" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.140625" style="63" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="63" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="18.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="22.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="18.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.42578125" style="38" bestFit="1" customWidth="1"/>
-    <col min="42" max="44" width="15" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="52" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="53" max="55" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="57" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="64" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5703125" style="64" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.5703125" style="65" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="13.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="68" max="70" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="63" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="18.85546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.42578125" style="38" bestFit="1" customWidth="1"/>
+    <col min="43" max="45" width="15" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="53" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="56" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="65" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.5703125" style="64" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="13.5703125" style="65" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.5703125" style="63" bestFit="1" customWidth="1"/>
+    <col min="69" max="71" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:74" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>2</v>
       </c>
@@ -1758,201 +1792,204 @@
       <c r="F1" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="88" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="L1" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="M1" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="N1" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="P1" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="S1" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="T1" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W1" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="S1" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="T1" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="U1" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="W1" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD1" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE1" s="20" t="s">
+      <c r="AG1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="AF1" s="21" t="s">
+      <c r="AH1" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="AG1" s="21" t="s">
+      <c r="AI1" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="AH1" s="32" t="s">
+      <c r="AJ1" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="AI1" s="32" t="s">
+      <c r="AK1" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="AJ1" s="44" t="s">
+      <c r="AL1" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="AK1" s="21" t="s">
+      <c r="AM1" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="AL1" s="21" t="s">
+      <c r="AN1" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="AM1" s="21" t="s">
+      <c r="AO1" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="AN1" s="21" t="s">
+      <c r="AP1" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="AO1" s="21" t="s">
+      <c r="AQ1" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="AP1" s="20" t="s">
+      <c r="AR1" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="AQ1" s="32" t="s">
+      <c r="AS1" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="AR1" s="32" t="s">
+      <c r="AT1" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AS1" s="32" t="s">
+      <c r="AU1" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="AT1" s="32" t="s">
+      <c r="AV1" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="AU1" s="32" t="s">
+      <c r="AW1" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="AV1" s="32" t="s">
+      <c r="AX1" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="AW1" s="32" t="s">
+      <c r="AY1" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="AX1" s="32" t="s">
+      <c r="AZ1" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="AY1" s="32" t="s">
+      <c r="BA1" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AZ1" s="32" t="s">
+      <c r="BB1" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="BA1" s="20" t="s">
+      <c r="BC1" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="BB1" s="32" t="s">
+      <c r="BD1" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="BC1" s="32" t="s">
+      <c r="BE1" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="BD1" s="32" t="s">
+      <c r="BF1" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="BE1" s="32" t="s">
+      <c r="BG1" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="BF1" s="32" t="s">
+      <c r="BH1" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="BG1" s="32" t="s">
+      <c r="BI1" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="BH1" s="32" t="s">
+      <c r="BJ1" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="BI1" s="32" t="s">
+      <c r="BK1" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="BJ1" s="32" t="s">
+      <c r="BL1" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="BK1" s="32" t="s">
+      <c r="BM1" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="BL1" s="33" t="s">
+      <c r="BN1" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="BM1" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="BN1" s="48" t="s">
+      <c r="BO1" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="BP1" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="49"/>
+      <c r="BT1" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="BO1" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="BP1" s="2"/>
-      <c r="BQ1" s="2"/>
-      <c r="BR1" s="49"/>
-      <c r="BS1" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="BT1" s="28"/>
-      <c r="BU1" s="51"/>
-    </row>
-    <row r="2" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU1" s="28"/>
+      <c r="BV1" s="51"/>
+    </row>
+    <row r="2" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" s="53">
         <v>70</v>
@@ -1970,158 +2007,161 @@
         <v>5.2</v>
       </c>
       <c r="G2" s="54">
-        <f t="shared" ref="G2" si="0">PI()/4*F2^2</f>
+        <v>1</v>
+      </c>
+      <c r="H2" s="54">
+        <f t="shared" ref="H2" si="0">PI()/4*F2^2</f>
         <v>21.237166338267002</v>
       </c>
-      <c r="H2" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="56">
-        <f t="shared" ref="I2:I3" si="1">9*845000</f>
+      <c r="I2" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="56">
+        <f t="shared" ref="J2:J3" si="1">9*845000</f>
         <v>7605000</v>
       </c>
-      <c r="J2" s="56">
-        <f t="shared" ref="J2:J3" si="2">9*845000*(312/283)</f>
+      <c r="K2" s="56">
+        <f t="shared" ref="K2:K3" si="2">9*845000*(312/283)</f>
         <v>8384310.9540636046</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="L2" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="M2" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="L2" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="M2" s="58">
+      <c r="N2" s="58">
         <f>421300-25600</f>
         <v>395700</v>
       </c>
-      <c r="N2" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="O2" s="59"/>
+      <c r="O2" s="59" t="s">
+        <v>149</v>
+      </c>
       <c r="P2" s="59"/>
-      <c r="Q2" s="58">
+      <c r="Q2" s="59"/>
+      <c r="R2" s="58">
         <v>25600</v>
       </c>
-      <c r="R2" s="58">
+      <c r="S2" s="58">
         <v>162</v>
       </c>
-      <c r="S2" s="60" t="b">
+      <c r="T2" s="60" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="T2" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="61">
-        <v>0</v>
+      <c r="U2" s="55" t="s">
+        <v>83</v>
       </c>
       <c r="V2" s="61">
         <v>0</v>
       </c>
-      <c r="W2" s="57" t="s">
+      <c r="W2" s="61">
+        <v>0</v>
+      </c>
+      <c r="X2" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y2" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="X2" s="57" t="s">
+      <c r="Z2" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="Y2" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z2" s="58">
+      <c r="AA2" s="58">
         <v>9.9999999999999994E-12</v>
       </c>
-      <c r="AA2" s="58"/>
       <c r="AB2" s="58"/>
-      <c r="AC2" s="58">
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="58">
         <v>9.9999999999999994E-12</v>
       </c>
-      <c r="AD2" s="58">
+      <c r="AE2" s="58">
         <v>9</v>
       </c>
-      <c r="AE2" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF2" s="61">
-        <v>981000</v>
+      <c r="AF2" s="70" t="s">
+        <v>83</v>
       </c>
       <c r="AG2" s="61">
         <v>981000</v>
       </c>
-      <c r="AH2" s="57" t="s">
+      <c r="AH2" s="61">
+        <v>981000</v>
+      </c>
+      <c r="AI2" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ2" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="AI2" s="57" t="s">
+      <c r="AK2" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="AJ2" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="AK2" s="58">
-        <f t="shared" ref="AK2" si="3">96600-3900</f>
+      <c r="AL2" s="58">
+        <f t="shared" ref="AL2" si="3">96600-3900</f>
         <v>92700</v>
       </c>
-      <c r="AL2" s="58"/>
       <c r="AM2" s="58"/>
-      <c r="AN2" s="58">
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="58">
         <v>3900</v>
       </c>
-      <c r="AO2" s="58">
+      <c r="AP2" s="58">
         <v>397</v>
       </c>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="61"/>
+      <c r="AQ2" s="55"/>
       <c r="AR2" s="61"/>
-      <c r="AS2" s="57"/>
+      <c r="AS2" s="61"/>
       <c r="AT2" s="57"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="58"/>
-      <c r="AW2" s="62"/>
+      <c r="AU2" s="57"/>
+      <c r="AV2" s="59"/>
+      <c r="AW2" s="58"/>
       <c r="AX2" s="62"/>
       <c r="AY2" s="62"/>
       <c r="AZ2" s="62"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="61"/>
+      <c r="BA2" s="62"/>
+      <c r="BB2" s="55"/>
       <c r="BC2" s="61"/>
-      <c r="BD2" s="57"/>
+      <c r="BD2" s="61"/>
       <c r="BE2" s="57"/>
-      <c r="BF2" s="58"/>
+      <c r="BF2" s="57"/>
       <c r="BG2" s="58"/>
       <c r="BH2" s="58"/>
       <c r="BI2" s="58"/>
       <c r="BJ2" s="58"/>
       <c r="BK2" s="58"/>
-      <c r="BL2" s="59"/>
-      <c r="BM2" s="62">
+      <c r="BL2" s="58"/>
+      <c r="BM2" s="59"/>
+      <c r="BN2" s="62">
         <v>549000</v>
       </c>
-      <c r="BN2" s="69">
+      <c r="BO2" s="69">
         <v>22800</v>
       </c>
-      <c r="BO2" s="69">
-        <f t="shared" ref="BO2" si="4">M2+Q2+Z2+AC2+AK2+AN2+AV2+AY2+BG2+BJ2</f>
+      <c r="BP2" s="69">
+        <f t="shared" ref="BP2" si="4">N2+R2+AA2+AD2+AL2+AO2+AW2+AZ2+BH2+BK2</f>
         <v>517900</v>
       </c>
-      <c r="BP2" s="69">
-        <f t="shared" ref="BP2" si="5">BM2-BO2</f>
+      <c r="BQ2" s="69">
+        <f t="shared" ref="BQ2" si="5">BN2-BP2</f>
         <v>31100</v>
       </c>
-      <c r="BQ2" s="71">
-        <f t="shared" ref="BQ2" si="6">BP2/BO2</f>
+      <c r="BR2" s="71">
+        <f t="shared" ref="BR2" si="6">BQ2/BP2</f>
         <v>6.0050202741842057E-2</v>
       </c>
-      <c r="BR2" s="72">
-        <f t="shared" ref="BR2" si="7">(I2/BO2+IF(S2=TRUE,U2/BO2,0))/9.81</f>
+      <c r="BS2" s="72">
+        <f t="shared" ref="BS2" si="7">(J2/BP2+IF(T2=TRUE,V2/BP2,0))/9.81</f>
         <v>1.4968707429970363</v>
       </c>
-      <c r="BS2" s="38">
-        <f>M2+Z2+AK2+AV2+BG2</f>
+      <c r="BT2" s="38">
+        <f>N2+AA2+AL2+AW2+BH2</f>
         <v>488400</v>
       </c>
-      <c r="BT2"/>
-    </row>
-    <row r="3" spans="1:73" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU2"/>
+    </row>
+    <row r="3" spans="1:74" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B3" s="53">
         <v>70</v>
@@ -2139,148 +2179,151 @@
         <v>5.2</v>
       </c>
       <c r="G3" s="54">
-        <f t="shared" ref="G3" si="8">PI()/4*F3^2</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="54">
+        <f t="shared" ref="H3" si="8">PI()/4*F3^2</f>
         <v>21.237166338267002</v>
       </c>
-      <c r="H3" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="56">
+      <c r="I3" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="56">
         <f t="shared" si="1"/>
         <v>7605000</v>
       </c>
-      <c r="J3" s="56">
+      <c r="K3" s="56">
         <f t="shared" si="2"/>
         <v>8384310.9540636046</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="L3" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="L3" s="57" t="s">
+      <c r="N3" s="58">
+        <f>S3/S2*N2</f>
+        <v>363946.29629629629</v>
+      </c>
+      <c r="O3" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="M3" s="58">
-        <f>R3/R2*M2</f>
-        <v>363946.29629629629</v>
-      </c>
-      <c r="N3" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="O3" s="58"/>
       <c r="P3" s="58"/>
-      <c r="Q3" s="58">
-        <f>Q2+M2*(1-R3/R2)</f>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58">
+        <f>R2+N2*(1-S3/S2)</f>
         <v>57353.703703703708</v>
       </c>
-      <c r="R3" s="58">
+      <c r="S3" s="58">
         <v>149</v>
       </c>
-      <c r="S3" s="60" t="b">
+      <c r="T3" s="60" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" s="61">
-        <v>0</v>
+      <c r="U3" s="55" t="s">
+        <v>83</v>
       </c>
       <c r="V3" s="61">
         <v>0</v>
       </c>
-      <c r="W3" s="57" t="s">
+      <c r="W3" s="61">
+        <v>0</v>
+      </c>
+      <c r="X3" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y3" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="X3" s="57" t="s">
+      <c r="Z3" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="Y3" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z3" s="58">
+      <c r="AA3" s="58">
         <v>9.9999999999999994E-12</v>
       </c>
-      <c r="AA3" s="58"/>
       <c r="AB3" s="58"/>
-      <c r="AC3" s="58">
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58">
         <v>9.9999999999999994E-12</v>
       </c>
-      <c r="AD3" s="58">
+      <c r="AE3" s="58">
         <v>9</v>
       </c>
-      <c r="AE3" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF3" s="61">
-        <v>981000</v>
+      <c r="AF3" s="70" t="s">
+        <v>83</v>
       </c>
       <c r="AG3" s="61">
         <v>981000</v>
       </c>
-      <c r="AH3" s="57" t="s">
+      <c r="AH3" s="61">
+        <v>981000</v>
+      </c>
+      <c r="AI3" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ3" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="AI3" s="57" t="s">
+      <c r="AK3" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="AJ3" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="AK3" s="58">
-        <f t="shared" ref="AK3" si="9">96600-3900</f>
+      <c r="AL3" s="58">
+        <f t="shared" ref="AL3" si="9">96600-3900</f>
         <v>92700</v>
       </c>
-      <c r="AL3" s="58"/>
       <c r="AM3" s="58"/>
-      <c r="AN3" s="58">
+      <c r="AN3" s="58"/>
+      <c r="AO3" s="58">
         <v>3900</v>
       </c>
-      <c r="AO3" s="58">
+      <c r="AP3" s="58">
         <v>397</v>
       </c>
-      <c r="AP3" s="55"/>
-      <c r="AQ3" s="61"/>
+      <c r="AQ3" s="55"/>
       <c r="AR3" s="61"/>
-      <c r="AS3" s="57"/>
+      <c r="AS3" s="61"/>
       <c r="AT3" s="57"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="58"/>
-      <c r="AW3" s="62"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="59"/>
+      <c r="AW3" s="58"/>
       <c r="AX3" s="62"/>
       <c r="AY3" s="62"/>
       <c r="AZ3" s="62"/>
-      <c r="BA3" s="55"/>
-      <c r="BB3" s="61"/>
+      <c r="BA3" s="62"/>
+      <c r="BB3" s="55"/>
       <c r="BC3" s="61"/>
-      <c r="BD3" s="57"/>
+      <c r="BD3" s="61"/>
       <c r="BE3" s="57"/>
-      <c r="BF3" s="58"/>
+      <c r="BF3" s="57"/>
       <c r="BG3" s="58"/>
       <c r="BH3" s="58"/>
       <c r="BI3" s="58"/>
       <c r="BJ3" s="58"/>
       <c r="BK3" s="58"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="62">
+      <c r="BL3" s="58"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="62">
         <v>549000</v>
       </c>
-      <c r="BN3" s="34"/>
-      <c r="BO3" s="69">
-        <f>M3+Q3+Z3+AC3+AK3+AN3+AV3+AY3+BG3+BJ3</f>
+      <c r="BO3" s="34"/>
+      <c r="BP3" s="69">
+        <f>N3+R3+AA3+AD3+AL3+AO3+AW3+AZ3+BH3+BK3</f>
         <v>517900</v>
       </c>
-      <c r="BP3" s="2"/>
       <c r="BQ3" s="2"/>
       <c r="BR3" s="2"/>
-      <c r="BS3" s="38">
-        <f>M3+Z3+AK3+AV3+BG3</f>
+      <c r="BS3" s="2"/>
+      <c r="BT3" s="38">
+        <f>N3+AA3+AL3+AW3+BH3</f>
         <v>456646.29629629629</v>
       </c>
-      <c r="BT3" s="2"/>
-      <c r="BU3" s="51"/>
-    </row>
-    <row r="4" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU3" s="2"/>
+      <c r="BV3" s="51"/>
+    </row>
+    <row r="4" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B4" s="53">
         <v>52</v>
@@ -2298,159 +2341,162 @@
         <v>5.4</v>
       </c>
       <c r="G4" s="54">
+        <v>1</v>
+      </c>
+      <c r="H4" s="54">
         <f>(F4^2+3^2*2)*PI()/4</f>
         <v>37.039377385823663</v>
       </c>
-      <c r="H4" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="I4" s="56">
+      <c r="I4" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="56">
         <f>2*3500000</f>
         <v>7000000</v>
       </c>
-      <c r="J4" s="56">
+      <c r="K4" s="56">
         <f>2*4600000</f>
         <v>9200000</v>
       </c>
-      <c r="K4" s="57" t="s">
+      <c r="L4" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="L4" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="M4" s="58">
+      <c r="N4" s="58">
         <f>2*(151500-9500)</f>
         <v>284000</v>
       </c>
-      <c r="N4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O4" s="59"/>
+      <c r="O4" s="59" t="s">
+        <v>155</v>
+      </c>
       <c r="P4" s="59"/>
-      <c r="Q4" s="58">
+      <c r="Q4" s="59"/>
+      <c r="R4" s="58">
         <f>2*9500</f>
         <v>19000</v>
       </c>
-      <c r="R4" s="58">
+      <c r="S4" s="58">
         <v>138</v>
       </c>
-      <c r="S4" s="60" t="b">
+      <c r="T4" s="60" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="T4" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="U4" s="61">
+      <c r="U4" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="V4" s="61">
         <v>960000</v>
       </c>
-      <c r="V4" s="61">
+      <c r="W4" s="61">
         <v>1371000</v>
       </c>
-      <c r="W4" s="57" t="s">
+      <c r="X4" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y4" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="X4" s="57" t="s">
+      <c r="Z4" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="Y4" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z4" s="58">
+      <c r="AA4" s="58">
         <f>189000-14800</f>
         <v>174200</v>
       </c>
-      <c r="AA4" s="58"/>
       <c r="AB4" s="58"/>
-      <c r="AC4" s="58">
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58">
         <v>14800</v>
       </c>
-      <c r="AD4" s="58">
+      <c r="AE4" s="58">
         <v>465</v>
       </c>
-      <c r="AE4" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF4" s="61">
-        <v>180000</v>
+      <c r="AF4" s="55" t="s">
+        <v>95</v>
       </c>
       <c r="AG4" s="61">
         <v>180000</v>
       </c>
-      <c r="AH4" s="57" t="s">
+      <c r="AH4" s="61">
+        <v>180000</v>
+      </c>
+      <c r="AI4" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ4" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="AI4" s="57" t="s">
+      <c r="AK4" t="s">
         <v>146</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK4" s="38">
+      <c r="AL4" s="38">
         <f>36500-5500</f>
         <v>31000</v>
       </c>
-      <c r="AN4" s="38">
+      <c r="AO4" s="38">
         <v>5500</v>
       </c>
-      <c r="AO4" s="38">
+      <c r="AP4" s="38">
         <v>760</v>
       </c>
-      <c r="AP4" s="55"/>
-      <c r="AQ4" s="61"/>
+      <c r="AQ4" s="55"/>
       <c r="AR4" s="61"/>
-      <c r="AS4" s="57"/>
+      <c r="AS4" s="61"/>
       <c r="AT4" s="57"/>
-      <c r="AU4" s="59"/>
-      <c r="AV4" s="58"/>
-      <c r="AW4" s="62"/>
+      <c r="AU4" s="57"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="58"/>
       <c r="AX4" s="62"/>
       <c r="AY4" s="62"/>
       <c r="AZ4" s="62"/>
-      <c r="BA4" s="55"/>
-      <c r="BB4" s="61"/>
+      <c r="BA4" s="62"/>
+      <c r="BB4" s="55"/>
       <c r="BC4" s="61"/>
-      <c r="BD4" s="57"/>
+      <c r="BD4" s="61"/>
       <c r="BE4" s="57"/>
-      <c r="BF4" s="58"/>
+      <c r="BF4" s="57"/>
       <c r="BG4" s="58"/>
       <c r="BH4" s="58"/>
       <c r="BI4" s="58"/>
       <c r="BJ4" s="58"/>
       <c r="BK4" s="58"/>
-      <c r="BL4" s="59"/>
-      <c r="BM4" s="62">
-        <f>BM6-2*151500</f>
+      <c r="BL4" s="58"/>
+      <c r="BM4" s="59"/>
+      <c r="BN4" s="62">
+        <f>BN6-2*151500</f>
         <v>-303000</v>
       </c>
-      <c r="BN4" s="69">
+      <c r="BO4" s="69">
         <v>10350</v>
       </c>
-      <c r="BO4" s="69">
-        <f>M4+Q4+Z4+AC4+AK4+AN4+AV4+AY4+BG4+BJ4</f>
+      <c r="BP4" s="69">
+        <f>N4+R4+AA4+AD4+AL4+AO4+AW4+AZ4+BH4+BK4</f>
         <v>528500</v>
       </c>
-      <c r="BP4" s="69">
-        <f t="shared" ref="BP4" si="10">BM4-BO4</f>
+      <c r="BQ4" s="69">
+        <f t="shared" ref="BQ4" si="10">BN4-BP4</f>
         <v>-831500</v>
       </c>
-      <c r="BQ4" s="71">
-        <f t="shared" ref="BQ4" si="11">BP4/BO4</f>
+      <c r="BR4" s="71">
+        <f t="shared" ref="BR4" si="11">BQ4/BP4</f>
         <v>-1.5733207190160832</v>
       </c>
-      <c r="BR4" s="72">
-        <f t="shared" ref="BR4" si="12">(I4/BO4+IF(S4=TRUE,U4/BO4,0))/9.81</f>
+      <c r="BS4" s="72">
+        <f t="shared" ref="BS4" si="12">(J4/BP4+IF(T4=TRUE,V4/BP4,0))/9.81</f>
         <v>1.5353205704988924</v>
       </c>
-      <c r="BS4" s="38">
-        <f t="shared" ref="BS4:BS7" si="13">M4+Z4+AK4+AV4+BG4</f>
+      <c r="BT4" s="38">
+        <f t="shared" ref="BT4:BT7" si="13">N4+AA4+AL4+AW4+BH4</f>
         <v>489200</v>
       </c>
-      <c r="BT4"/>
-    </row>
-    <row r="5" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU4"/>
+    </row>
+    <row r="5" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="53">
         <v>121.3</v>
@@ -2468,160 +2514,163 @@
         <v>9</v>
       </c>
       <c r="G5" s="54">
-        <f t="shared" ref="G5:G6" si="14">PI()/4*F5^2</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="54">
+        <f t="shared" ref="H5:H6" si="14">PI()/4*F5^2</f>
         <v>63.617251235193308</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="I5" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" s="56">
+        <f t="shared" ref="J5:J8" si="15">33*2260000</f>
+        <v>74580000</v>
+      </c>
+      <c r="K5" s="56">
+        <f t="shared" ref="K5:K8" si="16">J5*347/327</f>
+        <v>79141467.889908254</v>
+      </c>
+      <c r="L5" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="M5" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="N5" s="58">
+        <v>3400000</v>
+      </c>
+      <c r="O5" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="I5" s="56">
-        <f t="shared" ref="I5:I8" si="15">33*2260000</f>
-        <v>74580000</v>
-      </c>
-      <c r="J5" s="56">
-        <f t="shared" ref="J5:J8" si="16">I5*347/327</f>
-        <v>79141467.889908254</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="M5" s="58">
-        <v>3400000</v>
-      </c>
-      <c r="N5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="O5" s="59"/>
       <c r="P5" s="59"/>
-      <c r="Q5" s="58">
+      <c r="Q5" s="59"/>
+      <c r="R5" s="58">
         <v>275000</v>
       </c>
-      <c r="R5" s="58">
+      <c r="S5" s="58">
         <v>166</v>
       </c>
-      <c r="S5" s="60" t="b">
+      <c r="T5" s="60" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="T5" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="U5" s="61">
-        <f t="shared" ref="U5:U8" si="17">3*2260000</f>
+      <c r="U5" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="V5" s="61">
+        <f t="shared" ref="V5:V8" si="17">3*2260000</f>
         <v>6780000</v>
       </c>
-      <c r="V5" s="56">
-        <f>U5*347/327</f>
+      <c r="W5" s="56">
+        <f>V5*347/327</f>
         <v>7194678.8990825685</v>
       </c>
-      <c r="W5" s="57" t="s">
+      <c r="X5" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y5" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="X5" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y5" s="59" t="s">
+      <c r="Z5" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA5" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AB5" s="58"/>
+      <c r="AC5" s="58"/>
+      <c r="AD5" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AE5" s="58">
+        <v>10</v>
+      </c>
+      <c r="AF5" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="Z5" s="58">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AA5" s="58"/>
-      <c r="AB5" s="58"/>
-      <c r="AC5" s="58">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AD5" s="58">
-        <v>10</v>
-      </c>
-      <c r="AE5" s="70" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF5" s="61">
-        <f t="shared" ref="AF5:AF7" si="18">347/327*2260000*3+2530000*3</f>
+      <c r="AG5" s="61">
+        <f t="shared" ref="AG5:AG7" si="18">347/327*2260000*3+2530000*3</f>
         <v>14784678.899082568</v>
       </c>
-      <c r="AG5" s="61">
-        <f t="shared" ref="AG5:AG7" si="19">AF5</f>
+      <c r="AH5" s="61">
+        <f t="shared" ref="AH5:AH7" si="19">AG5</f>
         <v>14784678.899082568</v>
       </c>
-      <c r="AH5" s="57" t="s">
+      <c r="AI5" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ5" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="AI5" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ5" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK5" s="58">
+      <c r="AK5" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL5" s="58">
         <v>1200000</v>
       </c>
-      <c r="AL5" s="58"/>
       <c r="AM5" s="58"/>
-      <c r="AN5" s="58">
+      <c r="AN5" s="58"/>
+      <c r="AO5" s="58">
         <v>100000</v>
       </c>
-      <c r="AO5" s="58">
+      <c r="AP5" s="58">
         <v>390</v>
       </c>
-      <c r="AP5" s="55"/>
-      <c r="AQ5" s="61"/>
+      <c r="AQ5" s="55"/>
       <c r="AR5" s="61"/>
-      <c r="AS5" s="57"/>
+      <c r="AS5" s="61"/>
       <c r="AT5" s="57"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="58"/>
-      <c r="AW5" s="62"/>
+      <c r="AU5" s="57"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="58"/>
       <c r="AX5" s="62"/>
       <c r="AY5" s="62"/>
       <c r="AZ5" s="62"/>
-      <c r="BA5" s="55"/>
-      <c r="BB5" s="61"/>
+      <c r="BA5" s="62"/>
+      <c r="BB5" s="55"/>
       <c r="BC5" s="61"/>
-      <c r="BD5" s="57"/>
+      <c r="BD5" s="61"/>
       <c r="BE5" s="57"/>
-      <c r="BF5" s="58"/>
+      <c r="BF5" s="57"/>
       <c r="BG5" s="58"/>
       <c r="BH5" s="58"/>
       <c r="BI5" s="58"/>
       <c r="BJ5" s="58"/>
       <c r="BK5" s="58"/>
-      <c r="BL5" s="59"/>
-      <c r="BM5" s="62">
+      <c r="BL5" s="58"/>
+      <c r="BM5" s="59"/>
+      <c r="BN5" s="62">
         <v>5000000</v>
       </c>
-      <c r="BN5" s="69">
+      <c r="BO5" s="69">
         <v>15000</v>
       </c>
-      <c r="BO5" s="69">
-        <f>M5+Q5+Z5+AC5+AK5+AN5+AV5+AY5+BG5+BJ5</f>
+      <c r="BP5" s="69">
+        <f>N5+R5+AA5+AD5+AL5+AO5+AW5+AZ5+BH5+BK5</f>
         <v>4975000.0000019995</v>
       </c>
-      <c r="BP5" s="69">
-        <f t="shared" ref="BP5" si="20">BM5-BO5</f>
+      <c r="BQ5" s="69">
+        <f t="shared" ref="BQ5" si="20">BN5-BP5</f>
         <v>24999.99999800045</v>
       </c>
-      <c r="BQ5" s="71">
-        <f t="shared" ref="BQ5" si="21">BP5/BO5</f>
+      <c r="BR5" s="71">
+        <f t="shared" ref="BR5" si="21">BQ5/BP5</f>
         <v>5.0251256277367646E-3</v>
       </c>
-      <c r="BR5" s="72">
-        <f t="shared" ref="BR5" si="22">(I5/BO5+IF(S5=TRUE,U5/BO5,0))/9.81</f>
+      <c r="BS5" s="72">
+        <f t="shared" ref="BS5" si="22">(J5/BP5+IF(T5=TRUE,V5/BP5,0))/9.81</f>
         <v>1.528129946367311</v>
       </c>
-      <c r="BS5" s="38">
+      <c r="BT5" s="38">
         <f t="shared" si="13"/>
         <v>4600000.0000010002</v>
       </c>
-      <c r="BT5"/>
-    </row>
-    <row r="6" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU5"/>
+    </row>
+    <row r="6" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="53">
         <v>121.3</v>
@@ -2639,151 +2688,154 @@
         <v>9</v>
       </c>
       <c r="G6" s="54">
+        <v>1</v>
+      </c>
+      <c r="H6" s="54">
         <f t="shared" si="14"/>
         <v>63.617251235193308</v>
       </c>
-      <c r="H6" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="I6" s="56">
+      <c r="I6" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="56">
         <f t="shared" si="15"/>
         <v>74580000</v>
       </c>
-      <c r="J6" s="56">
+      <c r="K6" s="56">
         <f t="shared" si="16"/>
         <v>79141467.889908254</v>
       </c>
-      <c r="K6" s="57" t="s">
+      <c r="L6" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="M6" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="L6" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="M6" s="58">
-        <f>R6/R5*M5</f>
+      <c r="N6" s="58">
+        <f>S6/S5*N5</f>
         <v>3133734.9397590361</v>
       </c>
-      <c r="N6" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="O6" s="59"/>
+      <c r="O6" s="59" t="s">
+        <v>153</v>
+      </c>
       <c r="P6" s="59"/>
-      <c r="Q6" s="58">
-        <f>Q5+M5*(1-R6/R5)</f>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="58">
+        <f>R5+N5*(1-S6/S5)</f>
         <v>541265.06024096371</v>
       </c>
-      <c r="R6" s="58">
+      <c r="S6" s="58">
         <v>153</v>
       </c>
-      <c r="S6" s="60" t="b">
+      <c r="T6" s="60" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="T6" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="U6" s="61">
+      <c r="U6" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="V6" s="61">
         <f t="shared" si="17"/>
         <v>6780000</v>
       </c>
-      <c r="V6" s="56">
-        <f>U6*347/327</f>
+      <c r="W6" s="56">
+        <f>V6*347/327</f>
         <v>7194678.8990825685</v>
       </c>
-      <c r="W6" s="57" t="s">
+      <c r="X6" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y6" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="X6" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y6" s="59" t="s">
+      <c r="Z6" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA6" s="58">
+        <f>((N5/S5)/33)*3*AE6</f>
+        <v>16757.940854326396</v>
+      </c>
+      <c r="AB6" s="58"/>
+      <c r="AC6" s="58"/>
+      <c r="AD6" s="58">
+        <f>R6-AA6</f>
+        <v>524507.11938663735</v>
+      </c>
+      <c r="AE6" s="58">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="Z6" s="58">
-        <f>((M5/R5)/33)*3*AD6</f>
-        <v>16757.940854326396</v>
-      </c>
-      <c r="AA6" s="58"/>
-      <c r="AB6" s="58"/>
-      <c r="AC6" s="58">
-        <f>Q6-Z6</f>
-        <v>524507.11938663735</v>
-      </c>
-      <c r="AD6" s="58">
-        <v>9</v>
-      </c>
-      <c r="AE6" s="70" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF6" s="61">
+      <c r="AG6" s="61">
         <f t="shared" si="18"/>
         <v>14784678.899082568</v>
       </c>
-      <c r="AG6" s="61">
+      <c r="AH6" s="61">
         <f t="shared" si="19"/>
         <v>14784678.899082568</v>
       </c>
-      <c r="AH6" s="57" t="s">
+      <c r="AI6" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ6" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="AI6" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ6" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK6" s="58">
+      <c r="AK6" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL6" s="58">
         <v>1200000</v>
       </c>
-      <c r="AL6" s="58"/>
       <c r="AM6" s="58"/>
-      <c r="AN6" s="58">
+      <c r="AN6" s="58"/>
+      <c r="AO6" s="58">
         <v>100000</v>
       </c>
-      <c r="AO6" s="58">
+      <c r="AP6" s="58">
         <v>390</v>
       </c>
-      <c r="AP6" s="55"/>
-      <c r="AQ6" s="61"/>
+      <c r="AQ6" s="55"/>
       <c r="AR6" s="61"/>
-      <c r="AS6" s="57"/>
+      <c r="AS6" s="61"/>
       <c r="AT6" s="57"/>
-      <c r="AU6" s="59"/>
-      <c r="AV6" s="58"/>
-      <c r="AW6" s="62"/>
+      <c r="AU6" s="57"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="58"/>
       <c r="AX6" s="62"/>
       <c r="AY6" s="62"/>
       <c r="AZ6" s="62"/>
-      <c r="BA6" s="55"/>
-      <c r="BB6" s="61"/>
+      <c r="BA6" s="62"/>
+      <c r="BB6" s="55"/>
       <c r="BC6" s="61"/>
-      <c r="BD6" s="57"/>
+      <c r="BD6" s="61"/>
       <c r="BE6" s="57"/>
-      <c r="BF6" s="58"/>
+      <c r="BF6" s="57"/>
       <c r="BG6" s="58"/>
       <c r="BH6" s="58"/>
       <c r="BI6" s="58"/>
       <c r="BJ6" s="58"/>
       <c r="BK6" s="58"/>
-      <c r="BL6" s="59"/>
-      <c r="BM6" s="62"/>
-      <c r="BN6" s="69"/>
-      <c r="BO6" s="69">
-        <f>M6+Q6+Z6+AC6+AK6+AN6+AV6+AY6+BG6+BJ6</f>
+      <c r="BL6" s="58"/>
+      <c r="BM6" s="59"/>
+      <c r="BN6" s="62"/>
+      <c r="BO6" s="69"/>
+      <c r="BP6" s="69">
+        <f>N6+R6+AA6+AD6+AL6+AO6+AW6+AZ6+BH6+BK6</f>
         <v>5516265.0602409635</v>
       </c>
-      <c r="BP6" s="69"/>
-      <c r="BQ6" s="71"/>
-      <c r="BR6" s="72"/>
-      <c r="BS6" s="38">
+      <c r="BQ6" s="69"/>
+      <c r="BR6" s="71"/>
+      <c r="BS6" s="72"/>
+      <c r="BT6" s="38">
         <f t="shared" si="13"/>
         <v>4350492.8806133624</v>
       </c>
-      <c r="BT6"/>
-    </row>
-    <row r="7" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU6"/>
+    </row>
+    <row r="7" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="52" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7" s="53">
         <v>123.1</v>
@@ -2801,114 +2853,117 @@
         <v>9</v>
       </c>
       <c r="G7" s="54">
+        <v>1</v>
+      </c>
+      <c r="H7" s="54">
         <f>PI()/4*F8^2+(2.44*4.88)*4*0.5</f>
         <v>87.4316512351933</v>
       </c>
-      <c r="H7" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" s="56">
+      <c r="I7" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" s="56">
         <f t="shared" si="15"/>
         <v>74580000</v>
       </c>
-      <c r="J7" s="56">
+      <c r="K7" s="56">
         <f t="shared" si="16"/>
         <v>79141467.889908254</v>
       </c>
-      <c r="K7" s="57" t="s">
+      <c r="L7" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="M7" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="L7" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="M7" s="58">
+      <c r="N7" s="58">
         <v>3400000</v>
       </c>
-      <c r="N7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="O7" s="59"/>
+      <c r="O7" s="59" t="s">
+        <v>153</v>
+      </c>
       <c r="P7" s="59"/>
-      <c r="Q7" s="58">
+      <c r="Q7" s="59"/>
+      <c r="R7" s="58">
         <v>275000</v>
       </c>
-      <c r="R7" s="58">
+      <c r="S7" s="58">
         <v>166</v>
       </c>
-      <c r="S7" s="60" t="b">
+      <c r="T7" s="60" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="T7" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="U7" s="61">
+      <c r="U7" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="V7" s="61">
         <f t="shared" si="17"/>
         <v>6780000</v>
       </c>
-      <c r="V7" s="56">
-        <f>U7*347/327</f>
+      <c r="W7" s="56">
+        <f>V7*347/327</f>
         <v>7194678.8990825685</v>
       </c>
-      <c r="W7" s="57" t="s">
+      <c r="X7" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y7" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="X7" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y7" s="59" t="s">
+      <c r="Z7" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA7" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AB7" s="58"/>
+      <c r="AC7" s="58"/>
+      <c r="AD7" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AE7" s="58">
+        <v>10</v>
+      </c>
+      <c r="AF7" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="Z7" s="58">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="58"/>
-      <c r="AC7" s="58">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AD7" s="58">
-        <v>10</v>
-      </c>
-      <c r="AE7" s="70" t="s">
-        <v>155</v>
-      </c>
-      <c r="AF7" s="61">
+      <c r="AG7" s="61">
         <f t="shared" si="18"/>
         <v>14784678.899082568</v>
       </c>
-      <c r="AG7" s="61">
+      <c r="AH7" s="61">
         <f t="shared" si="19"/>
         <v>14784678.899082568</v>
       </c>
-      <c r="AH7" s="57" t="s">
+      <c r="AI7" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ7" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="AI7" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ7" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="AK7" s="58">
+      <c r="AK7" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL7" s="58">
         <v>1500000</v>
       </c>
-      <c r="AL7" s="58"/>
       <c r="AM7" s="58"/>
-      <c r="AN7" s="58">
+      <c r="AN7" s="58"/>
+      <c r="AO7" s="58">
         <v>85000</v>
       </c>
-      <c r="AO7" s="58">
+      <c r="AP7" s="58">
         <v>390</v>
       </c>
-      <c r="BS7" s="38">
+      <c r="BT7" s="38">
         <f t="shared" si="13"/>
         <v>4900000.0000010002</v>
       </c>
     </row>
-    <row r="8" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="53">
         <v>123.1</v>
@@ -2926,147 +2981,150 @@
         <v>9</v>
       </c>
       <c r="G8" s="54">
+        <v>1</v>
+      </c>
+      <c r="H8" s="54">
         <f>PI()/4*F8^2+(2.44*4.88)*4*0.5</f>
         <v>87.4316512351933</v>
       </c>
-      <c r="H8" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="I8" s="56">
+      <c r="I8" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" s="56">
         <f t="shared" si="15"/>
         <v>74580000</v>
       </c>
-      <c r="J8" s="56">
+      <c r="K8" s="56">
         <f t="shared" si="16"/>
         <v>79141467.889908254</v>
       </c>
-      <c r="K8" s="57" t="s">
+      <c r="L8" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="M8" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="L8" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="M8" s="58">
-        <f>R8/R7*M7</f>
+      <c r="N8" s="58">
+        <f>S8/S7*N7</f>
         <v>3133734.9397590361</v>
       </c>
-      <c r="N8" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="O8" s="59"/>
+      <c r="O8" s="59" t="s">
+        <v>153</v>
+      </c>
       <c r="P8" s="59"/>
-      <c r="Q8" s="58">
+      <c r="Q8" s="59"/>
+      <c r="R8" s="58">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="R8" s="58">
+      <c r="S8" s="58">
         <v>153</v>
       </c>
-      <c r="S8" s="60" t="b">
+      <c r="T8" s="60" t="b">
         <f>FALSE</f>
         <v>0</v>
       </c>
-      <c r="T8" s="55" t="s">
-        <v>153</v>
-      </c>
-      <c r="U8" s="61">
+      <c r="U8" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="V8" s="61">
         <f t="shared" si="17"/>
         <v>6780000</v>
       </c>
-      <c r="V8" s="56">
-        <f t="shared" ref="V8" si="23">U8*347/327</f>
+      <c r="W8" s="56">
+        <f t="shared" ref="W8" si="23">V8*347/327</f>
         <v>7194678.8990825685</v>
       </c>
-      <c r="W8" s="57" t="s">
+      <c r="X8" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y8" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="X8" s="57" t="s">
+      <c r="Z8" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA8" s="58">
+        <f>((N7/S7)/33)*3*AE8</f>
+        <v>13033.95399780942</v>
+      </c>
+      <c r="AB8" s="58"/>
+      <c r="AC8" s="58"/>
+      <c r="AD8" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="AE8" s="58">
+        <v>7</v>
+      </c>
+      <c r="AF8" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="Y8" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z8" s="58">
-        <f>((M7/R7)/33)*3*AD8</f>
-        <v>13033.95399780942</v>
-      </c>
-      <c r="AA8" s="58"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="58">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AD8" s="58">
-        <v>7</v>
-      </c>
-      <c r="AE8" s="70" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF8" s="61">
+      <c r="AG8" s="61">
         <f>2260000*3</f>
         <v>6780000</v>
       </c>
-      <c r="AG8" s="61">
+      <c r="AH8" s="61">
         <f>347/327*2260000*3</f>
         <v>7194678.8990825675</v>
       </c>
-      <c r="AH8" s="57" t="s">
+      <c r="AI8" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ8" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="AI8" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="AJ8" s="59" t="s">
+      <c r="AK8" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL8" s="58">
+        <f>((N7/S7)/33)*3*AP8+((AL7/AP7)/6)*6*AP8</f>
+        <v>11416.29454882467</v>
+      </c>
+      <c r="AM8" s="58"/>
+      <c r="AN8" s="58"/>
+      <c r="AO8" s="58">
+        <f>R7+N7-(N8+AA8+(((N7/S7)/33)*3*AP8))</f>
+        <v>524507.11938663758</v>
+      </c>
+      <c r="AP8" s="58">
+        <v>2</v>
+      </c>
+      <c r="AQ8" s="70" t="s">
         <v>154</v>
       </c>
-      <c r="AK8" s="58">
-        <f>((M7/R7)/33)*3*AO8+((AK7/AO7)/6)*6*AO8</f>
-        <v>11416.29454882467</v>
-      </c>
-      <c r="AL8" s="58"/>
-      <c r="AM8" s="58"/>
-      <c r="AN8" s="58">
-        <f>Q7+M7-(M8+Z8+(((M7/R7)/33)*3*AO8))</f>
-        <v>524507.11938663758</v>
-      </c>
-      <c r="AO8" s="58">
-        <v>2</v>
-      </c>
-      <c r="AP8" s="70" t="s">
-        <v>155</v>
-      </c>
-      <c r="AQ8" s="61">
+      <c r="AR8" s="61">
         <f>2260000*3+2530000*3</f>
         <v>14370000</v>
       </c>
-      <c r="AR8" s="61">
+      <c r="AS8" s="61">
         <f>347/327*2260000*3+2530000*3</f>
         <v>14784678.899082568</v>
       </c>
-      <c r="AS8" s="57" t="s">
+      <c r="AT8" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="AU8" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="AT8" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="AU8" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="AV8" s="58">
+      <c r="AV8" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW8" s="58">
         <v>1500000</v>
       </c>
-      <c r="AW8" s="58"/>
       <c r="AX8" s="58"/>
-      <c r="AY8" s="2">
+      <c r="AY8" s="58"/>
+      <c r="AZ8" s="2">
         <v>150000</v>
       </c>
-      <c r="AZ8" s="58">
+      <c r="BA8" s="58">
         <v>390</v>
       </c>
-      <c r="BO8" s="69">
-        <f>M8+Q8+Z8+AC8+AK8+AN8+AV8+AY8+BG8+BJ8</f>
+      <c r="BP8" s="69">
+        <f>N8+R8+AA8+AD8+AL8+AO8+AW8+AZ8+BH8+BK8</f>
         <v>5332692.3076943075</v>
       </c>
-      <c r="BS8" s="38">
-        <f>M8+Z8+AK8+AV8+BG8</f>
+      <c r="BT8" s="38">
+        <f>N8+AA8+AL8+AW8+BH8</f>
         <v>4658185.1883056704</v>
       </c>
     </row>
@@ -3076,90 +3134,90 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:S2 AE2:BL2 I3:J3">
+  <conditionalFormatting sqref="A2:T2 AF2:BM2 J3:K3">
     <cfRule type="cellIs" dxfId="19" priority="79" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:S8">
+  <conditionalFormatting sqref="A5:T8">
     <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:BL4">
+  <conditionalFormatting sqref="A4:BM4">
     <cfRule type="cellIs" dxfId="17" priority="53" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:S2 AE2:BK2 I3:J3">
+  <conditionalFormatting sqref="B2:T2 AF2:BL2 J3:K3">
     <cfRule type="containsBlanks" dxfId="16" priority="80">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:S8">
+  <conditionalFormatting sqref="B5:T8">
     <cfRule type="containsBlanks" dxfId="15" priority="14">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:BK4">
+  <conditionalFormatting sqref="B4:BL4">
     <cfRule type="containsBlanks" dxfId="14" priority="54">
       <formula>LEN(TRIM(B4))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:N3 V5:V8 AC8 AL8:AZ8">
+  <conditionalFormatting sqref="N3:O3 W5:W8 AD8 AM8:BA8">
     <cfRule type="cellIs" dxfId="13" priority="65" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="12" priority="66">
-      <formula>LEN(TRIM(M3))=0</formula>
+      <formula>LEN(TRIM(N3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
+  <conditionalFormatting sqref="R3">
     <cfRule type="cellIs" dxfId="11" priority="67" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="10" priority="68">
-      <formula>LEN(TRIM(Q3))=0</formula>
+      <formula>LEN(TRIM(R3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE8:AJ8">
+  <conditionalFormatting sqref="AF8:AK8">
     <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="8" priority="6">
-      <formula>LEN(TRIM(AE8))=0</formula>
+      <formula>LEN(TRIM(AF8))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE3:AO3">
+  <conditionalFormatting sqref="AF3:AP3">
     <cfRule type="cellIs" dxfId="7" priority="63" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="6" priority="64">
-      <formula>LEN(TRIM(AE3))=0</formula>
+      <formula>LEN(TRIM(AF3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE7:AO7">
+  <conditionalFormatting sqref="AF7:AP7">
     <cfRule type="cellIs" dxfId="5" priority="38" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="4" priority="39">
-      <formula>LEN(TRIM(AE7))=0</formula>
+      <formula>LEN(TRIM(AF7))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE5:BL6">
+  <conditionalFormatting sqref="AF5:BM6">
     <cfRule type="cellIs" dxfId="3" priority="34" operator="equal">
       <formula>0</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="2" priority="35">
-      <formula>LEN(TRIM(AE5))=0</formula>
+      <formula>LEN(TRIM(AF5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2">
+  <conditionalFormatting sqref="BR2">
     <cfRule type="cellIs" dxfId="1" priority="78" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ4:BQ6">
+  <conditionalFormatting sqref="BR4:BR6">
     <cfRule type="cellIs" dxfId="0" priority="52" operator="greaterThan">
       <formula>0.1</formula>
     </cfRule>
@@ -3174,18 +3232,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="2" max="2" width="6" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="10.5703125" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>65</v>
       </c>
@@ -3195,10 +3253,10 @@
       <c r="C1" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="21" t="s">
         <v>67</v>
       </c>
       <c r="F1" s="21" t="s">
@@ -3210,16 +3268,13 @@
       <c r="H1" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="J1" s="33" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="2">
         <v>140</v>
@@ -3227,23 +3282,20 @@
       <c r="C2" s="2">
         <v>100</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="35" t="s">
-        <v>73</v>
-      </c>
+      <c r="D2" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2">
         <v>70</v>
@@ -3251,23 +3303,20 @@
       <c r="C3" s="2">
         <v>100</v>
       </c>
-      <c r="D3" s="2">
-        <v>2</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>73</v>
-      </c>
+      <c r="D3" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2">
         <v>10</v>
@@ -3275,23 +3324,20 @@
       <c r="C4" s="2">
         <v>70</v>
       </c>
-      <c r="D4" s="2">
-        <v>2</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>73</v>
-      </c>
+      <c r="D4" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="36">
         <v>40</v>
@@ -3299,23 +3345,20 @@
       <c r="C5" s="2">
         <v>35</v>
       </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>73</v>
-      </c>
+      <c r="D5" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="2">
         <v>16</v>
@@ -3323,31 +3366,28 @@
       <c r="C6" s="2">
         <v>97</v>
       </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="81">
+      <c r="D6" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="81">
         <v>4.2767106842737095E-2</v>
       </c>
+      <c r="F6" s="74">
+        <v>0.3</v>
+      </c>
       <c r="G6" s="74">
-        <v>0.3</v>
-      </c>
-      <c r="H6" s="74">
         <v>1.36</v>
       </c>
-      <c r="I6" s="66">
+      <c r="H6" s="66">
         <v>200</v>
       </c>
-      <c r="J6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2">
         <v>165</v>
@@ -3355,31 +3395,28 @@
       <c r="C7" s="2">
         <v>97</v>
       </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="81">
+      <c r="D7" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="81">
         <v>4.2767106842737095E-2</v>
       </c>
+      <c r="F7" s="74">
+        <v>0.3</v>
+      </c>
       <c r="G7" s="74">
-        <v>0.3</v>
-      </c>
-      <c r="H7" s="74">
         <v>1.36</v>
       </c>
-      <c r="I7" s="66">
+      <c r="H7" s="66">
         <v>200</v>
       </c>
-      <c r="J7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2">
         <v>55</v>
@@ -3387,23 +3424,20 @@
       <c r="C8" s="2">
         <v>9</v>
       </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="82"/>
+      <c r="D8" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="82"/>
+      <c r="F8" s="75"/>
       <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="67"/>
-      <c r="J8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="67"/>
+      <c r="I8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="28">
         <v>14.71</v>
@@ -3411,18 +3445,15 @@
       <c r="C9" s="28">
         <v>105</v>
       </c>
-      <c r="D9" s="28">
-        <v>2</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="83"/>
+      <c r="D9" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="76"/>
       <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="68"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="68"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3432,23 +3463,20 @@
       <c r="C10" s="36">
         <v>70</v>
       </c>
-      <c r="D10" s="36">
-        <v>2</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="84"/>
+      <c r="D10" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="84"/>
+      <c r="F10" s="77"/>
       <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="36"/>
-      <c r="J10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="36"/>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2">
         <v>69</v>
@@ -3456,23 +3484,20 @@
       <c r="C11" s="2">
         <v>206</v>
       </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="85"/>
+      <c r="D11" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="85"/>
+      <c r="F11" s="78"/>
       <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="2"/>
-      <c r="J11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="2"/>
+      <c r="I11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="2">
         <v>8</v>
@@ -3480,23 +3505,20 @@
       <c r="C12" s="2">
         <v>46</v>
       </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="85"/>
+      <c r="D12" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="85"/>
+      <c r="F12" s="78"/>
       <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="2"/>
-      <c r="J12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="2"/>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="28">
         <v>240</v>
@@ -3504,17 +3526,14 @@
       <c r="C13" s="28">
         <v>60</v>
       </c>
-      <c r="D13" s="28">
-        <v>2</v>
-      </c>
-      <c r="E13" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="86"/>
+      <c r="D13" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="86"/>
+      <c r="F13" s="79"/>
       <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -3524,23 +3543,20 @@
       <c r="C14" s="2">
         <v>115</v>
       </c>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="35" t="s">
+      <c r="D14" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="85"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="2"/>
+      <c r="I14" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="85"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="2"/>
-      <c r="J14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="28">
         <v>58.2</v>
@@ -3548,32 +3564,29 @@
       <c r="C15" s="39">
         <v>118.8</v>
       </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="87">
+      <c r="D15" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="87">
         <f>5/326</f>
         <v>1.5337423312883436E-2</v>
       </c>
+      <c r="F15" s="80">
+        <v>0.9</v>
+      </c>
       <c r="G15" s="80">
-        <v>0.9</v>
-      </c>
-      <c r="H15" s="80">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I15" s="69">
+      <c r="H15" s="69">
         <v>130</v>
       </c>
-      <c r="J15" s="73" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I15" s="73" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B16" s="30">
         <v>11</v>
@@ -3581,21 +3594,20 @@
       <c r="C16">
         <v>90.5</v>
       </c>
-      <c r="D16"/>
-      <c r="E16" s="35" t="s">
-        <v>73</v>
-      </c>
+      <c r="D16" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="30">
         <v>34.340000000000003</v>
@@ -3603,16 +3615,13 @@
       <c r="C17" s="30">
         <v>350</v>
       </c>
-      <c r="D17" s="30">
-        <v>1.3</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="30">
         <v>80</v>
@@ -3620,16 +3629,13 @@
       <c r="C18" s="30">
         <v>350</v>
       </c>
-      <c r="D18" s="30">
-        <v>2.4</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B19" s="30">
         <v>48</v>
@@ -3637,11 +3643,10 @@
       <c r="C19">
         <v>177</v>
       </c>
-      <c r="D19"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B20">
         <v>35</v>
@@ -3649,13 +3654,10 @@
       <c r="C20">
         <v>180</v>
       </c>
-      <c r="D20">
-        <v>1.3380000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B21">
         <v>88</v>
@@ -3663,11 +3665,10 @@
       <c r="C21" s="30">
         <v>120</v>
       </c>
-      <c r="D21"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B22" s="30">
         <f>(69^2*PI()/4)/(9.5^2*PI()/4)</f>
@@ -3678,13 +3679,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J15">
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I15">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J15" r:id="rId1" display="https://www.eucass.eu/doi/EUCASS2019-0639.pdf" xr:uid="{EB873721-07AA-4E33-B1D0-17C38A00A309}"/>
+    <hyperlink ref="I15" r:id="rId1" display="https://www.eucass.eu/doi/EUCASS2019-0639.pdf" xr:uid="{EB873721-07AA-4E33-B1D0-17C38A00A309}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3695,7 +3696,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B1:F40"/>
+  <dimension ref="B1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4016,86 +4017,97 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="16" t="s">
-        <v>52</v>
+      <c r="B30" s="89" t="s">
+        <v>174</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="32" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
     </row>
     <row r="33" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="19" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+    </row>
+    <row r="34" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C34" s="29" t="s">
         <v>55</v>
-      </c>
-      <c r="D33" s="28"/>
-    </row>
-    <row r="34" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>57</v>
       </c>
       <c r="D34" s="28"/>
     </row>
     <row r="35" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="D35" s="28"/>
     </row>
     <row r="36" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="28"/>
+        <v>58</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>59</v>
+      </c>
       <c r="D36" s="28"/>
     </row>
     <row r="37" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
     </row>
     <row r="38" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
     </row>
     <row r="39" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
     </row>
     <row r="40" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
     </row>
+    <row r="41" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>